--- a/survey_templates/036_school_event_parent_feedback_questionnaire--survey_templates.xlsx
+++ b/survey_templates/036_school_event_parent_feedback_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'very_helpful'}</t>
+          <t>very_helpful</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Very Helpful'}</t>
+          <t>Very Helpful</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_helpful'}</t>
+          <t>somewhat_helpful</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Helpful'}</t>
+          <t>Somewhat Helpful</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_helpful'}</t>
+          <t>not_very_helpful</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Not Very Helpful'}</t>
+          <t>Not Very Helpful</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_helpful'}</t>
+          <t>not_at_all_helpful</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Not At All Helpful'}</t>
+          <t>Not At All Helpful</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'activity'}</t>
+          <t>activity</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Activity'}</t>
+          <t>Activity</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'class'}</t>
+          <t>class</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Class'}</t>
+          <t>Class</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'ongoing'}</t>
+          <t>ongoing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Ongoing'}</t>
+          <t>Ongoing</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'follow-up_sent'}</t>
+          <t>follow-up_sent</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Follow-up Sent'}</t>
+          <t>Follow-up Sent</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'not_sent'}</t>
+          <t>not_sent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sent'}</t>
+          <t>Not Sent</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'not_required'}</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Not Required'}</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'ongoing'}</t>
+          <t>ongoing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Ongoing'}</t>
+          <t>Ongoing</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
